--- a/docs/downloads/08/tbl_produits_elevage_marovoay_maroala.xlsx
+++ b/docs/downloads/08/tbl_produits_elevage_marovoay_maroala.xlsx
@@ -412,9 +412,6 @@
           <t>Henan'ondry</t>
         </is>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -517,9 +514,6 @@
           <t>Trondro Nompian</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -531,9 +525,6 @@
         <is>
           <t>Vorona</t>
         </is>
-      </c>
-      <c r="C12">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
